--- a/tasks/finalpool/canvas-course-comparison-excel/groundtruth_workspace/Course_Comparison_Fall2013.xlsx
+++ b/tasks/finalpool/canvas-course-comparison-excel/groundtruth_workspace/Course_Comparison_Fall2013.xlsx
@@ -470,7 +470,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
